--- a/src/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_1_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0015525409042896332</v>
       </c>
       <c r="B2">
-        <v>0.0014075081954164537</v>
+        <v>0.0011777321415815882</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0031050818085792665</v>
       </c>
       <c r="B3">
-        <v>0.0020872450825253222</v>
+        <v>0.0017705267380502372</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0046576227128689</v>
       </c>
       <c r="B4">
-        <v>0.002654071694745205</v>
+        <v>0.0022702835832048079</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0062101636171585329</v>
       </c>
       <c r="B5">
-        <v>0.0031421954649616625</v>
+        <v>0.002704378929951986</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0077627045214481655</v>
       </c>
       <c r="B6">
-        <v>0.0035655800009796695</v>
+        <v>0.0030839933585452557</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0093152454257378</v>
       </c>
       <c r="B7">
-        <v>0.00393220575874397</v>
+        <v>0.00341552014579638</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.010867786330027433</v>
       </c>
       <c r="B8">
-        <v>0.0042467748740914755</v>
+        <v>0.0037027295236978616</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.012420327234317066</v>
       </c>
       <c r="B9">
-        <v>0.0045166208764137973</v>
+        <v>0.00395149598725237</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.013972868138606698</v>
       </c>
       <c r="B10">
-        <v>0.0047496582892594136</v>
+        <v>0.0041681584143312628</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.015525409042896331</v>
       </c>
       <c r="B11">
-        <v>0.004953494219249577</v>
+        <v>0.0043588089512704752</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.017077949947185967</v>
       </c>
       <c r="B12">
-        <v>0.0051321973866251267</v>
+        <v>0.0045267086429795281</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.0186304908514756</v>
       </c>
       <c r="B13">
-        <v>0.0052759903830325019</v>
+        <v>0.0046640408601977</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B14">
-        <v>0.0053790306977468177</v>
+        <v>0.0047661364934864772</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.021735572660054867</v>
       </c>
       <c r="B15">
-        <v>0.0054650615391523116</v>
+        <v>0.00485199418686642</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.023288113564344497</v>
       </c>
       <c r="B16">
-        <v>0.00555586002971017</v>
+        <v>0.0049390393707132683</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.024840654468634132</v>
       </c>
       <c r="B17">
-        <v>0.0056357532290802568</v>
+        <v>0.0050147368673644039</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.026393195372923766</v>
       </c>
       <c r="B18">
-        <v>0.0056844977940008253</v>
+        <v>0.0050628947272429422</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.027945736277213397</v>
       </c>
       <c r="B19">
-        <v>0.00570101883232501</v>
+        <v>0.005082654521153307</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.029498277181503031</v>
       </c>
       <c r="B20">
-        <v>0.00568903356468466</v>
+        <v>0.0050769911999952446</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.031050818085792662</v>
       </c>
       <c r="B21">
-        <v>0.0056522592117116263</v>
+        <v>0.0050488797146685032</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.0326033589900823</v>
       </c>
       <c r="B22">
-        <v>0.0055937506618520295</v>
+        <v>0.0050007647662888418</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.034155899894371934</v>
       </c>
       <c r="B23">
-        <v>0.0055139134748090563</v>
+        <v>0.0049329700568360672</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.035708440798661568</v>
       </c>
       <c r="B24">
-        <v>0.0054124908781001645</v>
+        <v>0.0048452890385059962</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.0372609817029512</v>
       </c>
       <c r="B25">
-        <v>0.0052892260992428095</v>
+        <v>0.0047375151634944448</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.03881352260724083</v>
       </c>
       <c r="B26">
-        <v>0.0051437520212630683</v>
+        <v>0.0046093532362691961</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B27">
-        <v>0.0049752601492214958</v>
+        <v>0.0044601534703858723</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.0419186044158201</v>
       </c>
       <c r="B28">
-        <v>0.0047828316436872688</v>
+        <v>0.0042891774316720617</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.043471145320109733</v>
       </c>
       <c r="B29">
-        <v>0.0045655476652295647</v>
+        <v>0.0040956866859553492</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.045023686224399367</v>
       </c>
       <c r="B30">
-        <v>0.0043229801998542674</v>
+        <v>0.0038793350769650054</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.046576227128688995</v>
       </c>
       <c r="B31">
-        <v>0.0040566645353140984</v>
+        <v>0.0036413455600370205</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.048128768032978629</v>
       </c>
       <c r="B32">
-        <v>0.003768626784798482</v>
+        <v>0.0033833333684090642</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.049681308937268263</v>
       </c>
       <c r="B33">
-        <v>0.0034608930614968463</v>
+        <v>0.00310691373531881</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.0512338498415579</v>
       </c>
       <c r="B34">
-        <v>0.0031346923264200153</v>
+        <v>0.002813063760827753</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.052786390745847532</v>
       </c>
       <c r="B35">
-        <v>0.0027880649318643928</v>
+        <v>0.0025002080122926915</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.054338931650137159</v>
       </c>
       <c r="B36">
-        <v>0.0024182540779477822</v>
+        <v>0.0021661329238942474</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.055891472554426794</v>
       </c>
       <c r="B37">
-        <v>0.0020225029647879793</v>
+        <v>0.0018086249298130393</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.057444013458716428</v>
       </c>
       <c r="B38">
-        <v>0.0015961022937203981</v>
+        <v>0.0014239080801629247</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.058996554363006062</v>
       </c>
       <c r="B39">
-        <v>0.0011265327709508953</v>
+        <v>0.0010019568887906954</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B40">
-        <v>0.000599322603902939</v>
+        <v>0.00053118348547637737</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.062101636171585324</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>-1.5149413991730868E-20</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B43">
-        <v>-8.20685803626751E-05</v>
+        <v>-1.3929461936113648E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.058996554363006062</v>
       </c>
       <c r="B44">
-        <v>-0.00011922605065110416</v>
+        <v>5.3498315090958315E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.057444013458716428</v>
       </c>
       <c r="B45">
-        <v>-0.00012583984185433579</v>
+        <v>4.6354371703137566E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.055891472554426794</v>
       </c>
       <c r="B46">
-        <v>-0.00011627738496141928</v>
+        <v>9.7600650013520522E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.054338931650137159</v>
       </c>
       <c r="B47">
-        <v>-0.00010295746258756406</v>
+        <v>0.00014916369146597048</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.052786390745847532</v>
       </c>
       <c r="B48">
-        <v>-9.05042638526212E-05</v>
+        <v>0.00019735265571908017</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.0512338498415579</v>
       </c>
       <c r="B49">
-        <v>-8.1593329502601937E-05</v>
+        <v>0.00024003523608965972</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.049681308937268263</v>
       </c>
       <c r="B50">
-        <v>-7.8900200283517669E-05</v>
+        <v>0.00027507912589451867</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.048128768032978629</v>
       </c>
       <c r="B51">
-        <v>-8.4307379095689483E-05</v>
+        <v>0.00030098603729372756</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.046576227128688995</v>
       </c>
       <c r="B52">
-        <v>-9.6525217456677409E-05</v>
+        <v>0.00031879375782040007</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.045023686224399367</v>
       </c>
       <c r="B53">
-        <v>-0.00011347102903835116</v>
+        <v>0.00033017409385091063</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.043471145320109733</v>
       </c>
       <c r="B54">
-        <v>-0.00013306212751258061</v>
+        <v>0.00033679885176163385</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.0419186044158201</v>
       </c>
       <c r="B55">
-        <v>-0.00015371047646480391</v>
+        <v>0.00033994373555040335</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B56">
-        <v>-0.000175806639134733</v>
+        <v>0.00033930003970088994</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.03881352260724083</v>
       </c>
       <c r="B57">
-        <v>-0.00020023582867564825</v>
+        <v>0.00033416295631822349</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.0372609817029512</v>
       </c>
       <c r="B58">
-        <v>-0.00022788325824082991</v>
+        <v>0.00032382767750753423</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.035708440798661568</v>
       </c>
       <c r="B59">
-        <v>-0.00025952751784152385</v>
+        <v>0.00030767432175264527</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.034155899894371934</v>
       </c>
       <c r="B60">
-        <v>-0.00029552070492083629</v>
+        <v>0.00028542271305215326</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.0326033589900823</v>
       </c>
       <c r="B61">
-        <v>-0.00033610829377983894</v>
+        <v>0.00025687760178334806</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.031050818085792662</v>
       </c>
       <c r="B62">
-        <v>-0.00038153575871960349</v>
+        <v>0.0002218437383235197</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.029498277181503031</v>
       </c>
       <c r="B63">
-        <v>-0.00043139008220949141</v>
+        <v>0.00018065228247992376</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.027945736277213397</v>
       </c>
       <c r="B64">
-        <v>-0.000482624279392025</v>
+        <v>0.00013574003177967855</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.026393195372923766</v>
       </c>
       <c r="B65">
-        <v>-0.00053153287357801584</v>
+        <v>9.0070193179868352E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.024840654468634132</v>
       </c>
       <c r="B66">
-        <v>-0.00057441038807827624</v>
+        <v>4.6605973637577109E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.023288113564344497</v>
       </c>
       <c r="B67">
-        <v>-0.00061234656025883547</v>
+        <v>4.4740987380652439E-06</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.021735572660054867</v>
       </c>
       <c r="B68">
-        <v>-0.00066561198370659262</v>
+        <v>-5.2544631420701942E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B69">
-        <v>-0.00074991134485658331</v>
+        <v>-0.000137017140596243</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.0186304908514756</v>
       </c>
       <c r="B70">
-        <v>-0.0008435048453155165</v>
+        <v>-0.00023155532248071465</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.017077949947185967</v>
       </c>
       <c r="B71">
-        <v>-0.0009226900498308597</v>
+        <v>-0.000317201306185261</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.015525409042896331</v>
       </c>
       <c r="B72">
-        <v>-0.00099335846054143437</v>
+        <v>-0.00039867319256233326</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.013972868138606698</v>
       </c>
       <c r="B73">
-        <v>-0.001065340460022095</v>
+        <v>-0.000483840585093944</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.012420327234317066</v>
       </c>
       <c r="B74">
-        <v>-0.0011346280152004682</v>
+        <v>-0.00056950312603904157</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.010867786330027433</v>
       </c>
       <c r="B75">
-        <v>-0.0011936786298446613</v>
+        <v>-0.00064963327945104742</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0093152454257378</v>
       </c>
       <c r="B76">
-        <v>-0.0012346503707319292</v>
+        <v>-0.00071796475778433916</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0077627045214481655</v>
       </c>
       <c r="B77">
-        <v>-0.0012502864233644698</v>
+        <v>-0.00076869978093005583</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0062101636171585329</v>
       </c>
       <c r="B78">
-        <v>-0.0012359698851351025</v>
+        <v>-0.000798153350125426</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0046576227128689</v>
       </c>
       <c r="B79">
-        <v>-0.0011838094206587681</v>
+        <v>-0.0008000213091183707</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0031050818085792665</v>
       </c>
       <c r="B80">
-        <v>-0.0010799383622255288</v>
+        <v>-0.00076322001775044391</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0015525409042896332</v>
       </c>
       <c r="B81">
-        <v>-0.00089025234293220316</v>
+        <v>-0.00066047628909733755</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0018017730829636811</v>
       </c>
       <c r="B2">
-        <v>0.00068017281531712636</v>
+        <v>0.00054684160717781395</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0036035461659273621</v>
       </c>
       <c r="B3">
-        <v>0.0010212424996007136</v>
+        <v>0.0008374616451384179</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0054053192488910436</v>
       </c>
       <c r="B4">
-        <v>0.0013086172468803623</v>
+        <v>0.0010859180938260511</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0072070923318547243</v>
       </c>
       <c r="B5">
-        <v>0.0015581595904484386</v>
+        <v>0.0013041095857505595</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0090088654148184049</v>
       </c>
       <c r="B6">
-        <v>0.0017763356616885607</v>
+        <v>0.0014968873563151819</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.010810638497782087</v>
       </c>
       <c r="B7">
-        <v>0.0019668354558402684</v>
+        <v>0.001667020414835112</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.012612411580745768</v>
       </c>
       <c r="B8">
-        <v>0.0021318277828551013</v>
+        <v>0.0018161368192410798</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.014414184663709449</v>
       </c>
       <c r="B9">
-        <v>0.0022747044044395047</v>
+        <v>0.0019467817033401147</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.016215957746673129</v>
       </c>
       <c r="B10">
-        <v>0.0023991274744009912</v>
+        <v>0.002061702927486499</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.01801773082963681</v>
       </c>
       <c r="B11">
-        <v>0.0025086177631964321</v>
+        <v>0.0021635421823472277</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.019819503912600494</v>
       </c>
       <c r="B12">
-        <v>0.0026050541259830572</v>
+        <v>0.0022537096566283823</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.021621276995564175</v>
       </c>
       <c r="B13">
-        <v>0.0026838891400701686</v>
+        <v>0.0023287957008796861</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.023423050078527855</v>
       </c>
       <c r="B14">
-        <v>0.0027424026663367433</v>
+        <v>0.0023867610607308685</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.025224823161491536</v>
       </c>
       <c r="B15">
-        <v>0.0027916099777883945</v>
+        <v>0.0024358679002880459</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.027026596244455213</v>
       </c>
       <c r="B16">
-        <v>0.0028416142293353967</v>
+        <v>0.0024836942359471891</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.028828369327418897</v>
       </c>
       <c r="B17">
-        <v>0.0028851346913800384</v>
+        <v>0.0025247800747873021</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.030630142410382581</v>
       </c>
       <c r="B18">
-        <v>0.002912769726327299</v>
+        <v>0.0025520746648066864</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.032431915493346258</v>
       </c>
       <c r="B19">
-        <v>0.002924017949100913</v>
+        <v>0.0025652022269978176</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.034233688576309942</v>
       </c>
       <c r="B20">
-        <v>0.0029206030377543035</v>
+        <v>0.0025654557256017132</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.03603546165927362</v>
       </c>
       <c r="B21">
-        <v>0.0029042486703408942</v>
+        <v>0.0025541281248593916</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.037837234742237304</v>
       </c>
       <c r="B22">
-        <v>0.0028763716841241909</v>
+        <v>0.0025322821911353665</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.039639007825200988</v>
       </c>
       <c r="B23">
-        <v>0.0028371615532080327</v>
+        <v>0.0025000598992881372</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.041440780908164665</v>
       </c>
       <c r="B24">
-        <v>0.0027865009109063425</v>
+        <v>0.0024573730262997012</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.043242553991128349</v>
       </c>
       <c r="B25">
-        <v>0.00272427239053304</v>
+        <v>0.0024041333491520533</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.045044327074092026</v>
       </c>
       <c r="B26">
-        <v>0.0026503080066577118</v>
+        <v>0.0023402146159747094</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.04684610015705571</v>
       </c>
       <c r="B27">
-        <v>0.0025642372988725838</v>
+        <v>0.0022653384594872542</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.048647873240019388</v>
       </c>
       <c r="B28">
-        <v>0.0024656391880255482</v>
+        <v>0.0021791884835567934</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.050449646322983072</v>
       </c>
       <c r="B29">
-        <v>0.0023540925949644955</v>
+        <v>0.0020814482920504312</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.052251419405946756</v>
       </c>
       <c r="B30">
-        <v>0.0022294049141050572</v>
+        <v>0.0019719727786291393</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.054053192488910426</v>
       </c>
       <c r="B31">
-        <v>0.002092297434133833</v>
+        <v>0.0018513019961293549</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.05585496557187411</v>
       </c>
       <c r="B32">
-        <v>0.0019437199173051613</v>
+        <v>0.0017201472871813818</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.057656738654837794</v>
       </c>
       <c r="B33">
-        <v>0.0017846221258733832</v>
+        <v>0.0015792199944155237</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.059458511737801478</v>
       </c>
       <c r="B34">
-        <v>0.0016155844569721055</v>
+        <v>0.0014289543686455415</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.061260284820765162</v>
       </c>
       <c r="B35">
-        <v>0.0014357098472520015</v>
+        <v>0.0012686762934190211</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.063062057903728833</v>
       </c>
       <c r="B36">
-        <v>0.0012437318682430123</v>
+        <v>0.0010974345604670064</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.064863830986692517</v>
       </c>
       <c r="B37">
-        <v>0.0010383840914750761</v>
+        <v>0.00091427796152053779</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0666656040696562</v>
       </c>
       <c r="B38">
-        <v>0.00081749436289356111</v>
+        <v>0.0007175759329917375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.068467377152619885</v>
       </c>
       <c r="B39">
-        <v>0.000575267626105542</v>
+        <v>0.0005029804900170393</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.070269150235583569</v>
       </c>
       <c r="B40">
-        <v>0.00030500309913352065</v>
+        <v>0.0002654642924139556</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.072070923318547239</v>
       </c>
       <c r="B42">
-        <v>8.7906883089380759E-21</v>
+        <v>-7.8139451635005117E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.070269150235583569</v>
       </c>
       <c r="B43">
-        <v>-1.1307354622999208E-05</v>
+        <v>2.8231452096565772E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.068467377152619885</v>
       </c>
       <c r="B44">
-        <v>-3.0294626024798827E-06</v>
+        <v>6.9257673486022869E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0666656040696562</v>
       </c>
       <c r="B45">
-        <v>1.8146923678971751E-05</v>
+        <v>0.00011806535358079544</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.064863830986692517</v>
       </c>
       <c r="B46">
-        <v>4.5535051838769344E-05</v>
+        <v>0.00016964118179330773</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.063062057903728833</v>
       </c>
       <c r="B47">
-        <v>7.3353406034964291E-05</v>
+        <v>0.00021965071381097032</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.061260284820765162</v>
       </c>
       <c r="B48">
-        <v>9.9441416588158676E-05</v>
+        <v>0.00026647497042113911</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.059458511737801478</v>
       </c>
       <c r="B49">
-        <v>0.00012254375035959265</v>
+        <v>0.00030917383868615681</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.057656738654837794</v>
       </c>
       <c r="B50">
-        <v>0.000141405074210506</v>
+        <v>0.00034680720566836578</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.05585496557187411</v>
       </c>
       <c r="B51">
-        <v>0.00015513887631492354</v>
+        <v>0.00037871150643870337</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.054053192488910426</v>
       </c>
       <c r="B52">
-        <v>0.00016433393009800937</v>
+        <v>0.00040532936810248746</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.052251419405946756</v>
       </c>
       <c r="B53">
-        <v>0.0001699478302977126</v>
+        <v>0.00042737996577363086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.050449646322983072</v>
       </c>
       <c r="B54">
-        <v>0.00017293817165198232</v>
+        <v>0.00044558247456604659</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.048647873240019388</v>
       </c>
       <c r="B55">
-        <v>0.00017403355227550875</v>
+        <v>0.00046048425674426375</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.04684610015705571</v>
       </c>
       <c r="B56">
-        <v>0.00017304658378994721</v>
+        <v>0.00047194542317527681</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.045044327074092026</v>
       </c>
       <c r="B57">
-        <v>0.00016956088119369415</v>
+        <v>0.00047965427187669633</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.043242553991128349</v>
       </c>
       <c r="B58">
-        <v>0.00016316005948514614</v>
+        <v>0.00048329910086613291</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.041440780908164665</v>
       </c>
       <c r="B59">
-        <v>0.00015347783405321433</v>
+        <v>0.0004826057186598553</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.039639007825200988</v>
       </c>
       <c r="B60">
-        <v>0.0001403483218488687</v>
+        <v>0.0004774499757687642</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.037837234742237304</v>
       </c>
       <c r="B61">
-        <v>0.00012365574021359384</v>
+        <v>0.00046774523320241846</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.03603546165927362</v>
       </c>
       <c r="B62">
-        <v>0.00010328430648887446</v>
+        <v>0.00045340485197037692</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.034233688576309942</v>
       </c>
       <c r="B63">
-        <v>7.9424540533584368E-05</v>
+        <v>0.00043457185268617424</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.032431915493346258</v>
       </c>
       <c r="B64">
-        <v>5.3492172276153706E-05</v>
+        <v>0.00041230789437924861</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.030630142410382581</v>
       </c>
       <c r="B65">
-        <v>2.7209234162402017E-05</v>
+        <v>0.00038790429568301416</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.028828369327418897</v>
       </c>
       <c r="B66">
-        <v>2.2977586381485708E-06</v>
+        <v>0.00036265237523088481</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.027026596244455213</v>
       </c>
       <c r="B67">
-        <v>-2.1745717770263753E-05</v>
+        <v>0.0003361742756179439</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.025224823161491536</v>
       </c>
       <c r="B68">
-        <v>-5.4326642214398477E-05</v>
+        <v>0.00030141543528595076</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.023423050078527855</v>
       </c>
       <c r="B69">
-        <v>-0.00010273017851025762</v>
+        <v>0.00025291142709561758</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.021621276995564175</v>
       </c>
       <c r="B70">
-        <v>-0.00015685837345368961</v>
+        <v>0.00019823506573679269</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.019819503912600494</v>
       </c>
       <c r="B71">
-        <v>-0.00020570162885434094</v>
+        <v>0.00014564284050033388</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.01801773082963681</v>
       </c>
       <c r="B72">
-        <v>-0.00025198688359720159</v>
+        <v>9.3088697252002636E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.016215957746673129</v>
       </c>
       <c r="B73">
-        <v>-0.00030026890091494255</v>
+        <v>3.7155645999549168E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.014414184663709449</v>
       </c>
       <c r="B74">
-        <v>-0.00034867720435561515</v>
+        <v>-2.075450325622517E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.012612411580745768</v>
       </c>
       <c r="B75">
-        <v>-0.00039369992605707105</v>
+        <v>-7.8008962443049562E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.010810638497782087</v>
       </c>
       <c r="B76">
-        <v>-0.00043168487220098352</v>
+        <v>-0.00013186983119582707</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0090088654148184049</v>
       </c>
       <c r="B77">
-        <v>-0.00045925078129846887</v>
+        <v>-0.00017980247592509012</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0072070923318547243</v>
       </c>
       <c r="B78">
-        <v>-0.0004742404471345932</v>
+        <v>-0.00022019044243671416</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0054053192488910436</v>
       </c>
       <c r="B79">
-        <v>-0.00047297597755412575</v>
+        <v>-0.00025027682449981474</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0036035461659273621</v>
       </c>
       <c r="B80">
-        <v>-0.00044900433609765006</v>
+        <v>-0.00026522348163535452</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0018017730829636811</v>
       </c>
       <c r="B81">
-        <v>-0.00038647684979737279</v>
+        <v>-0.00025314564165806037</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0020183031755765233</v>
       </c>
       <c r="B2">
-        <v>0.00054622494501209624</v>
+        <v>0.0003968705100194336</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0040366063511530466</v>
       </c>
       <c r="B3">
-        <v>0.00080887911633993116</v>
+        <v>0.00060301219243112593</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.00605490952672957</v>
       </c>
       <c r="B4">
-        <v>0.00102773867230851</v>
+        <v>0.0007782763998072517</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0080732127023060932</v>
       </c>
       <c r="B5">
-        <v>0.0012161260599095475</v>
+        <v>0.00093154531215325787</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.010091515877882616</v>
       </c>
       <c r="B6">
-        <v>0.0013794697394206373</v>
+        <v>0.0010664384218382684</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.012109819053459141</v>
       </c>
       <c r="B7">
-        <v>0.0015208661503771312</v>
+        <v>0.0011850205019611976</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.014128122229035664</v>
       </c>
       <c r="B8">
-        <v>0.00164213388677843</v>
+        <v>0.001288504409022581</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.016146425404612186</v>
       </c>
       <c r="B9">
-        <v>0.0017461193171800652</v>
+        <v>0.0013787881392251379</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.018164728580188711</v>
       </c>
       <c r="B10">
-        <v>0.0018358961383561966</v>
+        <v>0.0014579212196528988</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B11">
-        <v>0.0019144195853993701</v>
+        <v>0.0015278741612129547</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.022201334931341757</v>
       </c>
       <c r="B12">
-        <v>0.0019832656256257089</v>
+        <v>0.0015896979422560702</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.024219638106918281</v>
       </c>
       <c r="B13">
-        <v>0.0020386116169272576</v>
+        <v>0.0016408444270846366</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.026237941282494803</v>
       </c>
       <c r="B14">
-        <v>0.0020781702395752917</v>
+        <v>0.0016797890068060708</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.028256244458071327</v>
       </c>
       <c r="B15">
-        <v>0.0021111940727820888</v>
+        <v>0.0017127002937962596</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.030274547633647848</v>
       </c>
       <c r="B16">
-        <v>0.0021461695384056238</v>
+        <v>0.0017452361100576384</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.032292850809224373</v>
       </c>
       <c r="B17">
-        <v>0.0021769785299456724</v>
+        <v>0.001773317894830368</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.0343111539848009</v>
       </c>
       <c r="B18">
-        <v>0.0021957212857552149</v>
+        <v>0.0017916792923625905</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.036329457160377422</v>
       </c>
       <c r="B19">
-        <v>0.0022019759519582567</v>
+        <v>0.0018000391496966496</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.038347760335953947</v>
       </c>
       <c r="B20">
-        <v>0.0021971901516215581</v>
+        <v>0.0017993626145734382</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B21">
-        <v>0.0021828115078118796</v>
+        <v>0.0017906148347338498</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.042384366687106989</v>
       </c>
       <c r="B22">
-        <v>0.0021600300184417714</v>
+        <v>0.0017745891863257001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.044402669862683514</v>
       </c>
       <c r="B23">
-        <v>0.0021290051808069378</v>
+        <v>0.001751391959124495</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.046420973038260038</v>
       </c>
       <c r="B24">
-        <v>0.0020896388670488724</v>
+        <v>0.0017209576713126628</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.048439276213836563</v>
       </c>
       <c r="B25">
-        <v>0.0020418329493090679</v>
+        <v>0.0016832208410726315</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.050457579389413081</v>
       </c>
       <c r="B26">
-        <v>0.0019854469290356089</v>
+        <v>0.0016380877187895926</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.052475882564989605</v>
       </c>
       <c r="B27">
-        <v>0.0019201708249029401</v>
+        <v>0.0015853514836597854</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.05449418574056613</v>
       </c>
       <c r="B28">
-        <v>0.0018456522848920957</v>
+        <v>0.0015247770470822116</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.056512488916142654</v>
       </c>
       <c r="B29">
-        <v>0.001761538956984112</v>
+        <v>0.0014561293204558726</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.058530792091719179</v>
       </c>
       <c r="B30">
-        <v>0.0016676705945250386</v>
+        <v>0.0013793012646470184</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B31">
-        <v>0.0015646553723209871</v>
+        <v>0.0012946980383908866</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.062567398442872221</v>
       </c>
       <c r="B32">
-        <v>0.0014532935705430837</v>
+        <v>0.0012028528498899624</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.064585701618448746</v>
       </c>
       <c r="B33">
-        <v>0.0013343854693624545</v>
+        <v>0.0011042989073467306</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.066604004794025271</v>
       </c>
       <c r="B34">
-        <v>0.0012084211975565795</v>
+        <v>0.0009993626299216094</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.0686223079696018</v>
       </c>
       <c r="B35">
-        <v>0.0010746502783283507</v>
+        <v>0.00088754328060674452</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.0706406111451783</v>
       </c>
       <c r="B36">
-        <v>0.00093201208348701328</v>
+        <v>0.00076813333335221568</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.072658914320754844</v>
       </c>
       <c r="B37">
-        <v>0.00077944598484181121</v>
+        <v>0.00064042526210810022</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.074677217496331369</v>
       </c>
       <c r="B38">
-        <v>0.00061513057313312871</v>
+        <v>0.000503204334320771</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.0766955206719079</v>
       </c>
       <c r="B39">
-        <v>0.00043420131482590471</v>
+        <v>0.00035322699142177475</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.078713823847484418</v>
       </c>
       <c r="B40">
-        <v>0.00023103289531621664</v>
+        <v>0.00018674246833895184</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.080732127023060929</v>
       </c>
       <c r="B41">
-        <v>1.4333904203873785E-16</v>
+        <v>1.4340906599674406E-16</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.078713823847484418</v>
       </c>
       <c r="B43">
-        <v>-3.4709666547372726E-05</v>
+        <v>9.580760429892191E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.0766955206719079</v>
       </c>
       <c r="B44">
-        <v>-5.1644625598875033E-05</v>
+        <v>2.9329697805254924E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.074677217496331369</v>
       </c>
       <c r="B45">
-        <v>-5.64268597410175E-05</v>
+        <v>5.5499379071340193E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.072658914320754844</v>
       </c>
       <c r="B46">
-        <v>-5.4678351560454312E-05</v>
+        <v>8.4342371173256572E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.0706406111451783</v>
       </c>
       <c r="B47">
-        <v>-5.1260417321771812E-05</v>
+        <v>0.00011261833281302563</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.0686223079696018</v>
       </c>
       <c r="B48">
-        <v>-4.7991708001285063E-05</v>
+        <v>0.0001391152897203208</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.066604004794025271</v>
       </c>
       <c r="B49">
-        <v>-4.5930208253241253E-05</v>
+        <v>0.00016312835938172882</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.064585701618448746</v>
       </c>
       <c r="B50">
-        <v>-4.61339027318876E-05</v>
+        <v>0.000183952659283836</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.062567398442872221</v>
       </c>
       <c r="B51">
-        <v>-4.9350753375643296E-05</v>
+        <v>0.00020108996727747776</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.0605490952672957</v>
       </c>
       <c r="B52">
-        <v>-5.5088631259615345E-05</v>
+        <v>0.00021486870267048498</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.058530792091719179</v>
       </c>
       <c r="B53">
-        <v>-6.2545384743082708E-05</v>
+        <v>0.00022582394513493743</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.056512488916142654</v>
       </c>
       <c r="B54">
-        <v>-7.0918862185324438E-05</v>
+        <v>0.00023449077434291492</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.05449418574056613</v>
       </c>
       <c r="B55">
-        <v>-7.9599141967212232E-05</v>
+        <v>0.00024127609584267241</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.052475882564989605</v>
       </c>
       <c r="B56">
-        <v>-8.8745222555988915E-05</v>
+        <v>0.00024607411868716588</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.050457579389413081</v>
       </c>
       <c r="B57">
-        <v>-9.8708332440490112E-05</v>
+        <v>0.00024865087780552645</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.048439276213836563</v>
       </c>
       <c r="B58">
-        <v>-0.00010983970010955134</v>
+        <v>0.00024877240812688523</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.046420973038260038</v>
       </c>
       <c r="B59">
-        <v>-0.00012244830736838627</v>
+        <v>0.00024623288836782351</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.044402669862683514</v>
       </c>
       <c r="B60">
-        <v>-0.00013667414928772036</v>
+        <v>0.00024093907239472272</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.042384366687106989</v>
       </c>
       <c r="B61">
-        <v>-0.00015261497425465707</v>
+        <v>0.0002328258578614144</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.040366063511530464</v>
       </c>
       <c r="B62">
-        <v>-0.00017036853065629986</v>
+        <v>0.00022182814242173009</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.038347760335953947</v>
       </c>
       <c r="B63">
-        <v>-0.00018977507066716084</v>
+        <v>0.00020805246638095896</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.036329457160377422</v>
       </c>
       <c r="B64">
-        <v>-0.00020964486161138685</v>
+        <v>0.0001922919406502204</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.0343111539848009</v>
       </c>
       <c r="B65">
-        <v>-0.00022853067460053321</v>
+        <v>0.00017551131879209146</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.032292850809224373</v>
       </c>
       <c r="B66">
-        <v>-0.00024498528074615541</v>
+        <v>0.0001586753543691492</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.030274547633647848</v>
       </c>
       <c r="B67">
-        <v>-0.00025943103168228816</v>
+        <v>0.00014150239666569709</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.028256244458071327</v>
       </c>
       <c r="B68">
-        <v>-0.00027976860113288393</v>
+        <v>0.00011872517785294476</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.026237941282494803</v>
       </c>
       <c r="B69">
-        <v>-0.00031211715704003429</v>
+        <v>8.6264075729186688E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.024219638106918281</v>
       </c>
       <c r="B70">
-        <v>-0.00034799152212846944</v>
+        <v>4.977566771415168E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.022201334931341757</v>
       </c>
       <c r="B71">
-        <v>-0.0003781404745921257</v>
+        <v>1.5427208777513381E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.020183031755765232</v>
       </c>
       <c r="B72">
-        <v>-0.00040485295971912392</v>
+        <v>-1.830753553270829E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.018164728580188711</v>
       </c>
       <c r="B73">
-        <v>-0.00043195337386359183</v>
+        <v>-5.39784551602938E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.016146425404612186</v>
       </c>
       <c r="B74">
-        <v>-0.00045786775054949835</v>
+        <v>-9.0536572594571125E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.014128122229035664</v>
       </c>
       <c r="B75">
-        <v>-0.00047964297975666351</v>
+        <v>-0.00012601350200081458</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.012109819053459141</v>
       </c>
       <c r="B76">
-        <v>-0.00049420774011846985</v>
+        <v>-0.00015836209170253627</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.010091515877882616</v>
       </c>
       <c r="B77">
-        <v>-0.00049871816607357687</v>
+        <v>-0.00018568684849120783</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0080732127023060932</v>
       </c>
       <c r="B78">
-        <v>-0.00049135842662819068</v>
+        <v>-0.00020677767887190105</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.00605490952672957</v>
       </c>
       <c r="B79">
-        <v>-0.00046903496269903964</v>
+        <v>-0.00021957269019778146</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0040366063511530466</v>
       </c>
       <c r="B80">
-        <v>-0.00042632242711290069</v>
+        <v>-0.00022045550320409543</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0020183031755765233</v>
       </c>
       <c r="B81">
-        <v>-0.00034990166494387997</v>
+        <v>-0.00020054722995121733</v>
       </c>
     </row>
     <row r="82" spans="1:2">
